--- a/BRS/BRS_FIXTURES_All_Emails.xlsx
+++ b/BRS/BRS_FIXTURES_All_Emails.xlsx
@@ -127,7 +127,7 @@
     <t>E1</t>
   </si>
   <si>
-    <t>2026-02-27 16:01:53</t>
+    <t>2026-02-26</t>
   </si>
   <si>
     <t>C:\Users\THADLOW\OneDrive - Axpo Services AG\Desktop\SHIPPING BROKER REPORTS\BRS\Emails\2026-02-27_160157__FW_ BRS - VLGC DAILY UPDATE - 26.02.26\2026-02-27_160157__FW_ BRS - VLGC DAILY UPDATE - 26.02.26.msg</t>
